--- a/data/trans_orig/P1405-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2012</t>
+          <t>Población con diagnóstico de colitis en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23330</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426668</t>
+          <t>426699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436151</t>
+          <t>436171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295491</t>
+          <t>297311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311238</t>
+          <t>311209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728335</t>
+          <t>727910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745350</t>
+          <t>745430</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402762</t>
+          <t>402370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416756</t>
+          <t>416713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326916</t>
+          <t>326729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336240</t>
+          <t>336065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734626</t>
+          <t>733093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>751597</t>
+          <t>750800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618107</t>
+          <t>617965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627410</t>
+          <t>627400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>260129</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>878021</t>
+          <t>877965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887609</t>
+          <t>887580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31431</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1142672</t>
+          <t>1142942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1155939</t>
+          <t>1155925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742255</t>
+          <t>744192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757939</t>
+          <t>758433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892300</t>
+          <t>1892963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912345</t>
+          <t>1912649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500834</t>
+          <t>499703</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509525</t>
+          <t>509517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739972</t>
+          <t>740515</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753862</t>
+          <t>754064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1245948</t>
+          <t>1243994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1261689</t>
+          <t>1261249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261502</t>
+          <t>261935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1071320</t>
+          <t>1071592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1091565</t>
+          <t>1091679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1336770</t>
+          <t>1336722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357680</t>
+          <t>1357987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>47565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82216</t>
+          <t>80247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73308</t>
+          <t>73359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112607</t>
+          <t>114591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3380241</t>
+          <t>3380205</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3403484</t>
+          <t>3403263</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3463516</t>
+          <t>3465485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3497612</t>
+          <t>3498167</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6855035</t>
+          <t>6853051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6894334</t>
+          <t>6894283</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2016</t>
+          <t>Población con diagnóstico de colitis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410829</t>
+          <t>411272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425192</t>
+          <t>425345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339230</t>
+          <t>340307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756059</t>
+          <t>755259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770800</t>
+          <t>770869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>16134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369245</t>
+          <t>369795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356504</t>
+          <t>356139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369267</t>
+          <t>369297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729690</t>
+          <t>730663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744765</t>
+          <t>745587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513241</t>
+          <t>513169</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157268</t>
+          <t>157452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165201</t>
+          <t>165199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675530</t>
+          <t>675418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685897</t>
+          <t>685974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1137744</t>
+          <t>1136731</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147564</t>
+          <t>1147538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>806365</t>
+          <t>805213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>819956</t>
+          <t>820043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1949264</t>
+          <t>1949198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965386</t>
+          <t>1965047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>20057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>27368</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>608391</t>
+          <t>607589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619100</t>
+          <t>619571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>718908</t>
+          <t>718187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>732246</t>
+          <t>732935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1333582</t>
+          <t>1331582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349830</t>
+          <t>1349709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>31687</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282278</t>
+          <t>281195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1050385</t>
+          <t>1050338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1068750</t>
+          <t>1069022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1334167</t>
+          <t>1337578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356104</t>
+          <t>1356227</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>37540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41979</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73127</t>
+          <t>73896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63355</t>
+          <t>63528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100258</t>
+          <t>102346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3345685</t>
+          <t>3348182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3369008</t>
+          <t>3369555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3458469</t>
+          <t>3457700</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3489617</t>
+          <t>3490282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6817060</t>
+          <t>6814972</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6853963</t>
+          <t>6853790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P1405-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>18761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426699</t>
+          <t>427753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436171</t>
+          <t>436035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297311</t>
+          <t>295693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311209</t>
+          <t>310919</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727910</t>
+          <t>728821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745430</t>
+          <t>745772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23715</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402370</t>
+          <t>401610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416713</t>
+          <t>416476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326729</t>
+          <t>327299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336065</t>
+          <t>336037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733093</t>
+          <t>733703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>750800</t>
+          <t>750989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617965</t>
+          <t>618075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627400</t>
+          <t>627429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>877965</t>
+          <t>876743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887580</t>
+          <t>887568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20530</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1142942</t>
+          <t>1140876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1155925</t>
+          <t>1155978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744192</t>
+          <t>742632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>758433</t>
+          <t>758564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1892963</t>
+          <t>1891318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912649</t>
+          <t>1911976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19731</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>25684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499703</t>
+          <t>500146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509517</t>
+          <t>509523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740515</t>
+          <t>739119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754064</t>
+          <t>753873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1243994</t>
+          <t>1245159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1261249</t>
+          <t>1261312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38329</t>
+          <t>36494</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261935</t>
+          <t>261370</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1071592</t>
+          <t>1071925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1091679</t>
+          <t>1092546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1336722</t>
+          <t>1338557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357987</t>
+          <t>1359504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>17251</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47565</t>
+          <t>47768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80247</t>
+          <t>81590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73359</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114591</t>
+          <t>112977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3380205</t>
+          <t>3379067</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3403263</t>
+          <t>3404659</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3465485</t>
+          <t>3464142</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3498167</t>
+          <t>3497964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6853051</t>
+          <t>6854665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6894283</t>
+          <t>6895818</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411272</t>
+          <t>410892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425345</t>
+          <t>425344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340307</t>
+          <t>339488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755259</t>
+          <t>755326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770869</t>
+          <t>770969</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16134</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369795</t>
+          <t>368701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356139</t>
+          <t>357310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369297</t>
+          <t>369243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730663</t>
+          <t>730155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745587</t>
+          <t>745160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513169</t>
+          <t>513735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157452</t>
+          <t>158603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165199</t>
+          <t>165208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>675418</t>
+          <t>675511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685974</t>
+          <t>685993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1136731</t>
+          <t>1136884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147538</t>
+          <t>1147576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>805213</t>
+          <t>805008</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820043</t>
+          <t>819929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1949198</t>
+          <t>1948289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965047</t>
+          <t>1965162</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27368</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>607589</t>
+          <t>608705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619571</t>
+          <t>619565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>718187</t>
+          <t>719370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>732935</t>
+          <t>732342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1331582</t>
+          <t>1333984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349709</t>
+          <t>1349914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31592</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281195</t>
+          <t>281671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1050338</t>
+          <t>1049138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1069022</t>
+          <t>1069245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337578</t>
+          <t>1336104</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1356227</t>
+          <t>1355974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37540</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41314</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73896</t>
+          <t>72203</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,47 +5474,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>81136</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>64331</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>102025</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>81136</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>63528</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>102346</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3348182</t>
+          <t>3347779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3369555</t>
+          <t>3369062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3457700</t>
+          <t>3459393</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3490282</t>
+          <t>3488444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,47 +5587,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6477</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6836182</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6815293</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6852987</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>98,83%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6477</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6836182</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6814972</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6853790</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
